--- a/rules/CORE-000741/positive/01/data/unit-test-coreid-FB1111-positive.xlsx
+++ b/rules/CORE-000741/positive/01/data/unit-test-coreid-FB1111-positive.xlsx
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -891,7 +889,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>PCLASS</t>
+          <t>PCLAS</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
